--- a/data/trans_orig/IP31KM02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23679</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19364</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27347</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25015</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19770</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29830</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52873</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>41106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60965</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13756</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18071</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21480</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16665</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26725</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>24060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>102867</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93186</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>111633</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>104392</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94460</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>113905</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>59,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>117133</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106200</t>
+          <t>88876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127065</t>
+          <t>105664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>200116</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205629</t>
+          <t>187919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236879</t>
+          <t>213328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54175</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45409</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63856</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>54907</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45394</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64839</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64826</t>
+          <t>48270</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75759</t>
+          <t>56642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>119734</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104380</t>
+          <t>89232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135630</t>
+          <t>114641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>127016</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>114505</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>138618</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>105593</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92988</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115880</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>133071</t>
+          <t>108668</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119225</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146995</t>
+          <t>118845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>238664</t>
+          <t>235684</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220505</t>
+          <t>219620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256304</t>
+          <t>251949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73110</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61508</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85621</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>67479</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57192</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>80084</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>66004</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65495</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93265</t>
+          <t>78823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>146899</t>
+          <t>139114</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129259</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165058</t>
+          <t>155178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157272</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>136749</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>174198</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>53,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>131321</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>92084</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>151703</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>155558</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132170</t>
+          <t>124463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174364</t>
+          <t>153888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>286879</t>
+          <t>295594</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241302</t>
+          <t>269706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316671</t>
+          <t>318738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>118023</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155472</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>142946</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>122564</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>182183</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>149441</t>
+          <t>117015</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130635</t>
+          <t>101449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172829</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>292387</t>
+          <t>251964</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262595</t>
+          <t>228820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337964</t>
+          <t>277852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>410834</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>384652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>434676</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>366321</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>318794</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>395379</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>403613</t>
+          <t>346615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>386977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>747858</t>
+          <t>744514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>839350</t>
+          <t>813442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>275990</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>252148</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>302172</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>286813</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>257755</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>334340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>250389</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>231231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341120</t>
+          <t>271593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>597926</t>
+          <t>526378</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>558517</t>
+          <t>491589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>650009</t>
+          <t>560517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
